--- a/bucks-board.xlsx
+++ b/bucks-board.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Provincial Events" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Community Events" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lodges" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Links" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Meta" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -14178,6 +14179,194 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>URL</t>
+        </is>
+      </c>
+      <c r="D1" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Show</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp Groups</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Example Lodge Social Group</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>https://chat.whatsapp.com/example</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Fictional example - for organising social events and lifts to meetings.</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>WhatsApp Groups</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Example Province Wide Chat</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>https://chat.whatsapp.com/example2</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Another fictional example.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Facebook Pages</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Buckinghamshire Freemasons</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/example</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Fictional example - the Province's public Facebook page.</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Websites</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Buckinghamshire PGL</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>https://buckspgl.org</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Fictional example - the Provincial Grand Lodge website.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Websites</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>United Grand Lodge of England</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>https://ugle.org.uk</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fictional example.</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -14209,7 +14398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14285,72 +14474,96 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>LODGES sheet - one row per lodge. Shown in the Lodges tab (sortable/searchable table) and the</t>
+          <t>LODGES sheet - one row per lodge. Used by THREE tabs:</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>Map tab (grouped by venue, geocoded live). Next Meeting should be a real date. Installation is</t>
+          <t xml:space="preserve"> - Lodges: full sortable/searchable directory table.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>Yes/No. Ceremony and Special Events show as highlighted badges when filled in.</t>
+          <t xml:space="preserve"> - Lodge Events: upcoming meetings only, soonest first, in a feed like the Events tabs.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> - Locations: lodges sharing the same address are grouped under one venue entry.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>META sheet - update the 'Last Updated' date in B1 whenever you make changes (shown in the app header).</t>
+          <t>Next Meeting should be a real date. Installation is Yes/No. Ceremony and Special Events</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr"/>
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>show as highlighted badges when filled in.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>PUBLISHING - save the file (keeping the name bucks-board.xlsx), then either commit &amp; push with</t>
-        </is>
-      </c>
+      <c r="A18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>GitHub Desktop, or on github.com use 'Add file' &gt; 'Upload files' and commit. The app updates on next load.</t>
+          <t>LINKS sheet - one row per link (WhatsApp group, Facebook page, website, etc). Category groups</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr"/>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>links together on the Links tab (e.g. all 'WhatsApp Groups' rows appear under one heading).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>The Map tab needs the site to be live on the internet (not opened as a local file) to fetch venue</t>
+          <t>Show = No hides a link without deleting it.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>locations from OpenStreetMap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
+      <c r="A22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>META sheet - update the 'Last Updated' date in B1 whenever you make changes (shown in the app header).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>PUBLISHING - save the file (keeping the name bucks-board.xlsx), then either commit &amp; push with</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>GitHub Desktop, or on github.com use 'Add file' &gt; 'Upload files' and commit. The app updates on next load.</t>
+        </is>
+      </c>
+    </row>
     <row r="27"/>
     <row r="28"/>
     <row r="29"/>
